--- a/SIMULATION/VALIDASI DATA/HASIL-VALIDASI/distribusi_summary.xlsx
+++ b/SIMULATION/VALIDASI DATA/HASIL-VALIDASI/distribusi_summary.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ringkasan Konsolidasi" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tabel 4.2 - Spasial LAMA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tabel 4.4 - Spasial V2" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -700,4 +702,336 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Luar Malang Raya</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>288 (79.3%)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>72 (19.8%)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3 (0.8%)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tempat Makan</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>479 (94.9%)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>22 (4.4%)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4 (0.8%)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wisata</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>47 (25.0%)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>114 (60.6%)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>22 (11.7%)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5 (2.7%)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>814 (77.1%)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>208 (19.7%)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>29 (2.7%)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5 (0.5%)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1056</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Kota Malang</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kabupaten Malang</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Kota Batu</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Luar Malang Raya</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Hotel</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>179 (38.3%)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>130 (27.8%)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>158 (33.8%)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tempat Makan</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>247 (19.2%)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>834 (64.8%)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>207 (16.1%)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wisata</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>88 (14.0%)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>407 (64.7%)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>134 (21.3%)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>514 (21.6%)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1371 (57.5%)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>499 (20.9%)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0 (0.0%)</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2384</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/SIMULATION/VALIDASI DATA/HASIL-VALIDASI/distribusi_summary.xlsx
+++ b/SIMULATION/VALIDASI DATA/HASIL-VALIDASI/distribusi_summary.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Ringkasan Konsolidasi" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tabel 4.2 - Spasial LAMA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Tabel 4.4 - Spasial V2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Tabel 4.4 - Spasial V2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,222 +479,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hotel Lama</t>
+          <t>Coffee Shop</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lama</t>
+          <t>V2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>hotel.xlsx</t>
+          <t>coffee.xlsx</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>363</v>
+        <v>424</v>
       </c>
       <c r="F2" t="n">
-        <v>288</v>
+        <v>169</v>
       </c>
       <c r="G2" t="n">
-        <v>72</v>
+        <v>188</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tempat Makan Lama</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Tempat Makan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Lama</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>tempat-makan.xlsx</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>505</v>
-      </c>
-      <c r="F3" t="n">
-        <v>479</v>
-      </c>
-      <c r="G3" t="n">
-        <v>22</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wisata Lama</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Wisata</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Lama</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>wisata.xlsx</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>188</v>
-      </c>
-      <c r="F4" t="n">
-        <v>47</v>
-      </c>
-      <c r="G4" t="n">
-        <v>114</v>
-      </c>
-      <c r="H4" t="n">
-        <v>22</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Hotel V2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Hotel</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>V2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>hotelv2.xlsx</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>467</v>
-      </c>
-      <c r="F5" t="n">
-        <v>179</v>
-      </c>
-      <c r="G5" t="n">
-        <v>130</v>
-      </c>
-      <c r="H5" t="n">
-        <v>158</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tempat Makan V2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Tempat Makan</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>V2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>tempat_makanV2.xlsx</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>1288</v>
-      </c>
-      <c r="F6" t="n">
-        <v>247</v>
-      </c>
-      <c r="G6" t="n">
-        <v>834</v>
-      </c>
-      <c r="H6" t="n">
-        <v>207</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Wisata V2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Wisata</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>V2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>tempat_wisataV2.xlsx</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>629</v>
-      </c>
-      <c r="F7" t="n">
-        <v>88</v>
-      </c>
-      <c r="G7" t="n">
-        <v>407</v>
-      </c>
-      <c r="H7" t="n">
-        <v>134</v>
-      </c>
-      <c r="I7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -710,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,22 +562,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>288 (79.3%)</t>
+          <t>169 (39.9%)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>72 (19.8%)</t>
+          <t>188 (44.3%)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3 (0.8%)</t>
+          <t>67 (15.8%)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -772,28 +586,28 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>363</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tempat Makan</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>479 (94.9%)</t>
+          <t>169 (39.9%)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>22 (4.4%)</t>
+          <t>188 (44.3%)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4 (0.8%)</t>
+          <t>67 (15.8%)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -802,233 +616,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wisata</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>47 (25.0%)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>114 (60.6%)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>22 (11.7%)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>5 (2.7%)</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>814 (77.1%)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>208 (19.7%)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>29 (2.7%)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>5 (0.5%)</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1056</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Kategori</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Kota Malang</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Kabupaten Malang</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Kota Batu</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Luar Malang Raya</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Hotel</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>179 (38.3%)</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>130 (27.8%)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>158 (33.8%)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tempat Makan</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>247 (19.2%)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>834 (64.8%)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>207 (16.1%)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wisata</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>88 (14.0%)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>407 (64.7%)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>134 (21.3%)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>514 (21.6%)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1371 (57.5%)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>499 (20.9%)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0 (0.0%)</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>2384</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
